--- a/datos/repositorio acta trimestral.xlsx
+++ b/datos/repositorio acta trimestral.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego\OneDrive\Desktop\trabajo\Trazabilidad_seguimiento\datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DiegoAntonioConstant\Desktop\TrazabilidadSeguimiento\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_1CEE0152576CA62EEF76E4345C5766F8A180CAD5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC4AA927-884D-4FC1-BEE7-A100BD8D5EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,12 +28,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="47">
   <si>
     <t>CEDI</t>
   </si>
@@ -171,6 +174,9 @@
   </si>
   <si>
     <t>TOALOMBO LLACA ROSA ISABEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS </t>
   </si>
 </sst>
 </file>
@@ -975,7 +981,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>25</v>

--- a/datos/repositorio acta trimestral.xlsx
+++ b/datos/repositorio acta trimestral.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DiegoAntonioConstant\Desktop\TrazabilidadSeguimiento\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC4AA927-884D-4FC1-BEE7-A100BD8D5EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D58CF42C-FAC1-47B3-BEA6-4C852BC21A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="48">
   <si>
     <t>CEDI</t>
   </si>
@@ -176,7 +176,10 @@
     <t>TOALOMBO LLACA ROSA ISABEL</t>
   </si>
   <si>
-    <t xml:space="preserve">CARLOS </t>
+    <t>CARMEN FIGUEROA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARMEN FIGUEROA	</t>
   </si>
 </sst>
 </file>
@@ -882,7 +885,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>25</v>
@@ -915,7 +918,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>25</v>
@@ -948,7 +951,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>25</v>
@@ -1014,7 +1017,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>25</v>
